--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2021_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2021_valparaiso.xlsx
@@ -1,46 +1,224 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="comunas" sheetId="1" r:id="rId1"/>
+    <sheet name="Comunas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comunas'!$A$1:$B$39</definedName>
+  </definedNames>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+  <si>
+    <t xml:space="preserve">Comuna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algarrobo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabildo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calle Larga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cartagena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casablanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catemu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Quisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Tabo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hijuelas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isla de Pascua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Fernandez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cruz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Ligua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llaillay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Andes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olmué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panquehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papudo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petorca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puchuncaví</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Putaendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quillota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilpué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quintero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rinconada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Antonio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Esteban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Felipe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa María</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santo Domingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valparaíso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villa Alemana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viña del Mar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zapallar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha de creación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27 20:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIT - MDSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagen asociada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comunal_e_rezmat_a_2021_valparaiso.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porcentaje de rezago respecto a la población matriculada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valparaíso (Comunal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00135A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,21 +226,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -112,10 +306,6 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -141,15 +331,12 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -175,6 +362,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,397 +538,396 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Comuna</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Algarrobo</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>4.2461</v>
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>4.25</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cabildo</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>4.193062</v>
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>4.19</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Calera</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Calle Larga</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>4.255319</v>
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>4.26</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Cartagena</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>5.523475</v>
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>5.52</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Casablanca</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>4.621072</v>
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>4.62</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Catemu</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>6.228956</v>
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>6.23</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Concón</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>3.471122</v>
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>3.47</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>El Quisco</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>3.884712</v>
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>3.88</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>El Tabo</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>5.177848</v>
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>5.18</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Hijuelas</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>4.325537</v>
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Isla de Pascua</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>3.621582</v>
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>3.62</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Juan Fernandez</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>3.636364</v>
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>3.64</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>La Cruz</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>3.190153</v>
+      <c r="A15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>3.19</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>La Ligua</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>3.402291</v>
+      <c r="A16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Limache</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>5.388831</v>
+      <c r="A17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>5.39</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Llaillay</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="2"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Los Andes</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>4.112386</v>
+      <c r="A19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>4.11</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Nogales</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>3.330511</v>
+      <c r="A20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>3.33</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Olmué</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>5.202727</v>
+      <c r="A21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>5.2</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Panquehue</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>4.455446</v>
+      <c r="A22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>4.46</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Papudo</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>4.290092</v>
+      <c r="A23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>4.29</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Petorca</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>1.939799</v>
+      <c r="A24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>1.94</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Puchuncaví</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>6.308685</v>
+      <c r="A25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>6.31</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Putaendo</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>5.025308</v>
+      <c r="A26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>5.03</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Quillota</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>5.636014</v>
+      <c r="A27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>5.64</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Quilpué</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>4.693441</v>
+      <c r="A28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>4.69</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Quintero</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>6.372085</v>
+      <c r="A29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>6.37</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Rinconada</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>3.75134</v>
+      <c r="A30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>3.75</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>3.760521</v>
+      <c r="A31" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>3.76</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>San Esteban</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>3.753846</v>
+      <c r="A32" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>3.75</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>San Felipe</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>4.84443</v>
+      <c r="A33" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>4.84</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Santa María</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>5.462698</v>
+      <c r="A34" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>5.46</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Santo Domingo</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>2.795359</v>
+      <c r="A35" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>5.472661</v>
+      <c r="A36" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>5.47</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Villa Alemana</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>4.957479</v>
+      <c r="A37" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>4.96</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Viña del Mar</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>5.314109</v>
+      <c r="A38" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>5.31</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Zapallar</t>
-        </is>
-      </c>
-      <c r="B39">
-        <v>3.499563</v>
+      <c r="A39" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B39"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="60.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2021_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2021_valparaiso.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comunas'!$A$1:$B$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comunas'!$A$1:$B$37</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t xml:space="preserve">Comuna</t>
   </si>
@@ -30,9 +30,6 @@
     <t xml:space="preserve">Cabildo</t>
   </si>
   <si>
-    <t xml:space="preserve">Calera</t>
-  </si>
-  <si>
     <t xml:space="preserve">Calle Larga</t>
   </si>
   <si>
@@ -72,9 +69,6 @@
     <t xml:space="preserve">Limache</t>
   </si>
   <si>
-    <t xml:space="preserve">Llaillay</t>
-  </si>
-  <si>
     <t xml:space="preserve">Los Andes</t>
   </si>
   <si>
@@ -147,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 20:05</t>
+    <t xml:space="preserve">2026-08-03 09:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -574,14 +568,16 @@
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="2" t="n">
+        <v>4.26</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4.26</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="6">
@@ -589,7 +585,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5.52</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="7">
@@ -597,7 +593,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4.62</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="8">
@@ -605,7 +601,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6.23</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="9">
@@ -613,7 +609,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>3.47</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="10">
@@ -621,7 +617,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3.88</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="11">
@@ -629,7 +625,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>5.18</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="12">
@@ -637,7 +633,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>4.33</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="13">
@@ -645,7 +641,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="14">
@@ -653,7 +649,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>3.64</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="15">
@@ -661,7 +657,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>3.19</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="16">
@@ -669,7 +665,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>3.4</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="17">
@@ -677,21 +673,23 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>5.39</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="2"/>
+      <c r="B18" s="2" t="n">
+        <v>3.33</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>4.11</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="20">
@@ -699,7 +697,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>3.33</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="21">
@@ -707,7 +705,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>5.2</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="22">
@@ -715,7 +713,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>4.46</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="23">
@@ -723,7 +721,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>4.29</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="24">
@@ -731,7 +729,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>1.94</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="25">
@@ -739,7 +737,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>6.31</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="26">
@@ -747,7 +745,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>5.03</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="27">
@@ -755,7 +753,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>5.64</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="28">
@@ -763,7 +761,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>4.69</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="29">
@@ -771,7 +769,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>6.37</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="30">
@@ -787,7 +785,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>3.76</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="32">
@@ -795,7 +793,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>3.75</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="33">
@@ -803,7 +801,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>4.84</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="34">
@@ -811,7 +809,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>5.46</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="35">
@@ -819,7 +817,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>2.8</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="36">
@@ -827,7 +825,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>5.47</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="37">
@@ -835,27 +833,11 @@
         <v>37</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>4.96</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>5.31</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="2" t="n">
         <v>3.5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B39"/>
+  <autoFilter ref="A1:B37"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -872,58 +854,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2021_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2021_valparaiso.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-03 09:36</t>
+    <t xml:space="preserve">2026-08-05 10:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2021_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2021_valparaiso.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:46</t>
+    <t xml:space="preserve">2026-08-16 09:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2021_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2021_valparaiso.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:56</t>
+    <t xml:space="preserve">2026-08-19 12:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2021_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2021_valparaiso.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 12:51</t>
+    <t xml:space="preserve">2026-08-28 11:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2021_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2021_valparaiso.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:46</t>
+    <t xml:space="preserve">2026-09-06 17:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
